--- a/deliverables/gbp-calendars/Preferred-Fence-GBP-Monthly-Calendar-Nov-2026.xlsx
+++ b/deliverables/gbp-calendars/Preferred-Fence-GBP-Monthly-Calendar-Nov-2026.xlsx
@@ -11,11 +11,12 @@
     <sheet name="preferredfencesolutions.com" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Settings" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Banner &amp; Brand Kit" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="GBP Guidelines" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="QA Cross-Check" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Image Rights Check" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="GBP Guidelines" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="QA Cross-Check" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'preferredfencesolutions.com'!$B$1:$P$23</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'preferredfencesolutions.com'!$B$1:$Q$23</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="355">
   <si>
     <t xml:space="preserve">Week</t>
   </si>
@@ -66,6 +67,9 @@
   </si>
   <si>
     <t xml:space="preserve">Banner Photo Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Image Rights</t>
   </si>
   <si>
     <t xml:space="preserve">Offer Dates / Terms</t>
@@ -93,15 +97,17 @@
   <si>
     <t xml:space="preserve">Tag: Fence Repair
 Headline: Storm-Damaged Fence? We Rebuild It.
-Labels: Before, After
+Sub-line: Repairs and rebuilds across the OKC metro
 Button: Free Repair Estimate</t>
   </si>
   <si>
     <t xml:space="preserve">2026-11-02_gbp-post-01_1200x900.png</t>
   </si>
   <si>
-    <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2026/03/fence-damage.jpg
-https://preferredfencesolutions.com/wp-content/uploads/2021/12/IMG_5914.jpg</t>
+    <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2021/12/IMG_5914.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business's own photo from its website (client to confirm ownership).</t>
   </si>
   <si>
     <t xml:space="preserve">Not Published</t>
@@ -550,7 +556,7 @@
     <t xml:space="preserve">2026-11-27_gbp-post-20_1200x900.png</t>
   </si>
   <si>
-    <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2026/03/fence-damage.jpg</t>
+    <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/11/IMG_0730001.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Offer dates: Nov 27 to Dec 31, 2026. Terms: free estimate within the service area; no obligation.</t>
@@ -904,15 +910,153 @@
     <t xml:space="preserve">Split photo, offer card, FAQ question, local spotlight, glass panel, 3-up compare, diagonal, frame, before/after, project spotlight, seasonal thank-you.</t>
   </si>
   <si>
+    <t xml:space="preserve">Image rights cross-check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every banner photo is either the business's own photo from its website or a free Unsplash photo. Checked Oct 26, 2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Origin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence checked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verdict</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG_5914.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the preferredfencesolutions.com media library (wp-content/uploads); No photographer credit, stock agency tag or watermark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK: business's own photo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG_5904.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stained-Western-Red-Cedar-with-Cap-and-Trim-with-a-1x6-Kickboard.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG_01991-2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-tall-Cap-and-Trim-Total-Privacy-Board-on-Board.-.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">new-vs-old.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arched-ornamental-iron-double-gate-custom-Letter-2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG_8799-scaled.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG_5922.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4800-S-Sunnylane-Rd_Completed-Pic-5-scaled.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bassethound-doggie-window.jpeg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-black-chain-link.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1x4x6-Western-Red-Cedar-with-Cap-and-Trim-scaled.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG_5879.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6-tall-white-vinyl-privacy-fence-.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">desing-and-planning.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o-3.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o-8.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG_0730001.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG_5862.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG_5887.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2021/12/IMG_5887.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG_5911.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/04/IMG_5911.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o-2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/07/o-2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photos OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photos removed during the check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photo removed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replaced with</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fence-damage.jpg (2 banners)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No camera data, uploaded in 2026 and sized 1376 x 768, which matches AI-generated images; origin cannot be confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG_5914.jpg and IMG_0730001.jpg (own project photos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note: photos on the business's own website are treated as owned by the business. Ask the client to confirm they took these photos or hold the rights. Unsplash photos can be used commercially without credit, but do not show people or brands in a way that suggests endorsement.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Google Business Profile post rules applied to this calendar</t>
   </si>
   <si>
     <t xml:space="preserve">Every post and banner was written and checked against these rules.</t>
   </si>
   <si>
-    <t xml:space="preserve">#</t>
-  </si>
-  <si>
     <t xml:space="preserve">How this calendar follows it</t>
   </si>
   <si>
@@ -1016,9 +1160,6 @@
   </si>
   <si>
     <t xml:space="preserve">Formulas re-check every post when copy or links change. Every row should read Pass before scheduling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
   </si>
   <si>
     <t xml:space="preserve">Characters</t>
@@ -2395,7 +2536,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:P23"/>
+  <dimension ref="B1:Q23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -2412,8 +2553,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2462,6 +2603,9 @@
       <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="n">
@@ -2475,19 +2619,19 @@
         <v>Mon</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="5" t="str">
         <f aca="false">I2&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C13</f>
@@ -2495,17 +2639,20 @@
       </c>
       <c r="K2" s="4"/>
       <c r="L2" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="2" t="s">
         <v>23</v>
+      </c>
+      <c r="O2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="4"/>
+      <c r="Q2" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2520,19 +2667,19 @@
         <v>Tue</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J3" s="5" t="str">
         <f aca="false">I3&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C14</f>
@@ -2540,19 +2687,22 @@
       </c>
       <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2567,19 +2717,19 @@
         <v>Wed</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">I4&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C15</f>
@@ -2587,17 +2737,20 @@
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2612,19 +2765,19 @@
         <v>Thu</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J5" s="5" t="str">
         <f aca="false">I5&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C16</f>
@@ -2632,17 +2785,20 @@
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="O5" s="4"/>
-      <c r="P5" s="2" t="s">
-        <v>23</v>
+        <v>48</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2657,19 +2813,19 @@
         <v>Fri</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="J6" s="5" t="str">
         <f aca="false">I6&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C17</f>
@@ -2677,17 +2833,20 @@
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="O6" s="4"/>
-      <c r="P6" s="2" t="s">
-        <v>23</v>
+        <v>54</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2702,19 +2861,19 @@
         <v>Mon</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J7" s="5" t="str">
         <f aca="false">I7&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C18</f>
@@ -2722,17 +2881,20 @@
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="2" t="s">
-        <v>23</v>
+        <v>60</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2747,19 +2909,19 @@
         <v>Tue</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J8" s="5" t="str">
         <f aca="false">I8&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C19</f>
@@ -2767,17 +2929,20 @@
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="O8" s="4"/>
-      <c r="P8" s="2" t="s">
-        <v>23</v>
+        <v>66</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2792,19 +2957,19 @@
         <v>Wed</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J9" s="5" t="str">
         <f aca="false">I9&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C20</f>
@@ -2812,17 +2977,20 @@
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="O9" s="4"/>
-      <c r="P9" s="2" t="s">
-        <v>23</v>
+        <v>72</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2837,19 +3005,19 @@
         <v>Thu</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J10" s="5" t="str">
         <f aca="false">I10&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C21</f>
@@ -2857,17 +3025,20 @@
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="O10" s="4"/>
-      <c r="P10" s="2" t="s">
-        <v>23</v>
+        <v>78</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2882,19 +3053,19 @@
         <v>Fri</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="J11" s="5" t="str">
         <f aca="false">I11&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C22</f>
@@ -2902,17 +3073,20 @@
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="O11" s="4"/>
-      <c r="P11" s="2" t="s">
-        <v>23</v>
+        <v>84</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2927,19 +3101,19 @@
         <v>Mon</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J12" s="5" t="str">
         <f aca="false">I12&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C23</f>
@@ -2947,17 +3121,20 @@
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="O12" s="4"/>
-      <c r="P12" s="2" t="s">
-        <v>23</v>
+        <v>90</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2972,19 +3149,19 @@
         <v>Tue</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J13" s="5" t="str">
         <f aca="false">I13&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C24</f>
@@ -2992,17 +3169,20 @@
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="O13" s="4"/>
-      <c r="P13" s="2" t="s">
-        <v>23</v>
+        <v>96</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3017,19 +3197,19 @@
         <v>Wed</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J14" s="5" t="str">
         <f aca="false">I14&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C25</f>
@@ -3037,17 +3217,20 @@
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="O14" s="4"/>
-      <c r="P14" s="2" t="s">
-        <v>23</v>
+        <v>101</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3062,19 +3245,19 @@
         <v>Thu</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J15" s="5" t="str">
         <f aca="false">I15&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C26</f>
@@ -3082,17 +3265,20 @@
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="O15" s="4"/>
-      <c r="P15" s="2" t="s">
-        <v>23</v>
+        <v>107</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3107,19 +3293,19 @@
         <v>Fri</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J16" s="5" t="str">
         <f aca="false">I16&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C27</f>
@@ -3127,17 +3313,20 @@
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="O16" s="4"/>
-      <c r="P16" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3152,19 +3341,19 @@
         <v>Mon</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J17" s="5" t="str">
         <f aca="false">I17&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C28</f>
@@ -3172,19 +3361,22 @@
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3199,19 +3391,19 @@
         <v>Tue</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J18" s="5" t="str">
         <f aca="false">I18&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C29</f>
@@ -3219,17 +3411,20 @@
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="O18" s="4"/>
-      <c r="P18" s="2" t="s">
-        <v>23</v>
+        <v>126</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3244,19 +3439,19 @@
         <v>Wed</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J19" s="5" t="str">
         <f aca="false">I19&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C30</f>
@@ -3264,17 +3459,20 @@
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="O19" s="4"/>
-      <c r="P19" s="2" t="s">
-        <v>23</v>
+        <v>101</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3289,19 +3487,19 @@
         <v>Thu</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J20" s="5" t="str">
         <f aca="false">I20&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C31</f>
@@ -3309,17 +3507,20 @@
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="O20" s="4"/>
-      <c r="P20" s="2" t="s">
-        <v>23</v>
+        <v>137</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3334,19 +3535,19 @@
         <v>Fri</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J21" s="5" t="str">
         <f aca="false">I21&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C32</f>
@@ -3354,19 +3555,22 @@
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3381,19 +3585,19 @@
         <v>Mon</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J22" s="5" t="str">
         <f aca="false">I22&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C33</f>
@@ -3401,17 +3605,20 @@
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="O22" s="4"/>
-      <c r="P22" s="2" t="s">
-        <v>23</v>
+        <v>149</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="199.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3426,19 +3633,19 @@
         <v>Tue</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J23" s="5" t="str">
         <f aca="false">I23&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C34</f>
@@ -3446,23 +3653,26 @@
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="O23" s="4"/>
-      <c r="P23" s="2" t="s">
-        <v>23</v>
+        <v>155</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:P23"/>
+  <autoFilter ref="B1:Q23"/>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P23" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="Q2:Q23" type="list">
       <formula1>"Not Published,Scheduled,Published"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3492,80 +3702,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>4</v>
@@ -3576,7 +3786,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D13" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F2</f>
@@ -3588,7 +3798,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D14" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F3</f>
@@ -3600,7 +3810,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D15" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F4</f>
@@ -3612,7 +3822,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D16" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F5</f>
@@ -3624,7 +3834,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D17" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F6</f>
@@ -3636,7 +3846,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D18" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F7</f>
@@ -3648,7 +3858,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D19" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F8</f>
@@ -3660,7 +3870,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D20" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F9</f>
@@ -3672,7 +3882,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D21" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F10</f>
@@ -3684,7 +3894,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D22" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F11</f>
@@ -3696,7 +3906,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D23" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F12</f>
@@ -3708,7 +3918,7 @@
         <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D24" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F13</f>
@@ -3720,7 +3930,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D25" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F14</f>
@@ -3732,7 +3942,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D26" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F15</f>
@@ -3744,7 +3954,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D27" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F16</f>
@@ -3756,7 +3966,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D28" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F17</f>
@@ -3768,7 +3978,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D29" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F18</f>
@@ -3780,7 +3990,7 @@
         <v>18</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D30" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F19</f>
@@ -3792,7 +4002,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D31" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F20</f>
@@ -3804,7 +4014,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D32" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F21</f>
@@ -3816,7 +4026,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D33" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F22</f>
@@ -3828,7 +4038,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D34" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F23</f>
@@ -3864,232 +4074,232 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F17" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
   </sheetData>
@@ -4108,219 +4318,648 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>256</v>
+        <v>174</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>258</v>
+        <v>260</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>259</v>
+      <c r="B5" s="3" t="n">
+        <v>46328</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>23</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>262</v>
+      <c r="B6" s="3" t="n">
+        <v>46329</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>264</v>
+      <c r="B7" s="3" t="n">
+        <v>46330</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G7" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="n">
+        <v>46331</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>270</v>
+      <c r="B9" s="3" t="n">
+        <v>46332</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>271</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="n">
+        <v>46335</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>273</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>274</v>
+        <v>60</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>275</v>
+      <c r="B11" s="3" t="n">
+        <v>46336</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>66</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>277</v>
+      <c r="B12" s="3" t="n">
+        <v>46337</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>279</v>
+        <v>72</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>280</v>
+      <c r="B13" s="3" t="n">
+        <v>46338</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>279</v>
+        <v>78</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>282</v>
+      <c r="B14" s="3" t="n">
+        <v>46339</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>279</v>
+        <v>84</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>284</v>
+      <c r="B15" s="3" t="n">
+        <v>46342</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>286</v>
+      <c r="B16" s="3" t="n">
+        <v>46343</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>261</v>
+        <v>96</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="n">
+        <v>46344</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>46345</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>46346</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>46349</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>46351</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>46352</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>46353</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>46356</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>46357</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="E26" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>46357</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>269</v>
+      <c r="D27" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>46357</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="B30" s="9" t="str">
+        <f aca="false">COUNTIF(G5:G28,"OK*")&amp;" of "&amp;COUNTA(G5:G28)</f>
+        <v>24 of 24</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
@@ -4335,6 +4974,237 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -4356,53 +5226,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>290</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>291</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>292</v>
+        <v>258</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>293</v>
+        <v>340</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>294</v>
+        <v>341</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>295</v>
+        <v>342</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>296</v>
+        <v>343</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>297</v>
+        <v>344</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>299</v>
+        <v>346</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>300</v>
+        <v>347</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>301</v>
+        <v>348</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>302</v>
+        <v>349</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5573,7 +6443,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>304</v>
+        <v>351</v>
       </c>
       <c r="B28" s="9" t="str">
         <f aca="false">COUNTIF(M5:M26,"Pass")&amp;" of "&amp;COUNTA(A5:A26)</f>
@@ -5582,7 +6452,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>305</v>
+        <v>352</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5590,12 +6460,12 @@
         <v>3</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>306</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B32" s="2" t="n">
         <f aca="false">COUNTIF('preferredfencesolutions.com'!$E$2:$E$23,"Service")</f>
@@ -5604,7 +6474,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B33" s="2" t="n">
         <f aca="false">COUNTIF('preferredfencesolutions.com'!$E$2:$E$23,"FAQ")</f>
@@ -5613,7 +6483,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B34" s="2" t="n">
         <f aca="false">COUNTIF('preferredfencesolutions.com'!$E$2:$E$23,"Local")</f>
@@ -5622,7 +6492,7 @@
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B35" s="2" t="n">
         <f aca="false">COUNTIF('preferredfencesolutions.com'!$E$2:$E$23,"Promotional")</f>
@@ -5631,7 +6501,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>307</v>
+        <v>354</v>
       </c>
       <c r="B36" s="2" t="n">
         <f aca="false">SUM(B32:B35)</f>

--- a/deliverables/gbp-calendars/Preferred-Fence-GBP-Monthly-Calendar-Nov-2026.xlsx
+++ b/deliverables/gbp-calendars/Preferred-Fence-GBP-Monthly-Calendar-Nov-2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="359">
   <si>
     <t xml:space="preserve">Week</t>
   </si>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">2026-11-02_gbp-post-01_1200x900.png</t>
   </si>
   <si>
-    <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2021/12/IMG_5914.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business's own photo from its website (client to confirm ownership).</t>
+    <t xml:space="preserve">https://unsplash.com/photos/km_VQEFOV20 (Unsplash licence)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsplash License: free for commercial use, no permission or credit needed.</t>
   </si>
   <si>
     <t xml:space="preserve">Not Published</t>
@@ -139,7 +139,10 @@
     <t xml:space="preserve">2026-11-03_gbp-post-02_1200x900.png</t>
   </si>
   <si>
-    <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2021/12/IMG_5904.jpg</t>
+    <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/05/IMG_5913.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business's own photo from its website (client to confirm ownership).</t>
   </si>
   <si>
     <t xml:space="preserve">Offer dates: Nov 3 to Nov 30, 2026. Terms: free estimate within the service area; no obligation.</t>
@@ -556,7 +559,7 @@
     <t xml:space="preserve">2026-11-27_gbp-post-20_1200x900.png</t>
   </si>
   <si>
-    <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/11/IMG_0730001.jpg</t>
+    <t xml:space="preserve">https://unsplash.com/photos/LbkIbkMPKjg (Unsplash licence)</t>
   </si>
   <si>
     <t xml:space="preserve">Offer dates: Nov 27 to Dec 31, 2026. Terms: free estimate within the service area; no obligation.</t>
@@ -582,7 +585,7 @@
     <t xml:space="preserve">2026-11-30_gbp-post-21_1200x900.png</t>
   </si>
   <si>
-    <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/07/IMG_5862.jpg</t>
+    <t xml:space="preserve">https://unsplash.com/photos/0WxjDT_3Tsw (Unsplash licence)</t>
   </si>
   <si>
     <t xml:space="preserve">Thank You, Oklahoma City</t>
@@ -934,7 +937,19 @@
     <t xml:space="preserve">Verdict</t>
   </si>
   <si>
-    <t xml:space="preserve">IMG_5914.jpg</t>
+    <t xml:space="preserve">unsplash_km_VQEFOV20.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unsplash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downloaded through the official Unsplash API; free photo, not Unsplash+; No photographer credit, stock agency tag or watermark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK: royalty-free (Unsplash License)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IMG_5913.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Business website</t>
@@ -946,9 +961,6 @@
     <t xml:space="preserve">OK: business's own photo</t>
   </si>
   <si>
-    <t xml:space="preserve">IMG_5904.jpg</t>
-  </si>
-  <si>
     <t xml:space="preserve">Stained-Western-Red-Cedar-with-Cap-and-Trim-with-a-1x6-Kickboard.jpg</t>
   </si>
   <si>
@@ -997,10 +1009,10 @@
     <t xml:space="preserve">o-8.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">IMG_0730001.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IMG_5862.jpg</t>
+    <t xml:space="preserve">unsplash_LbkIbkMPKjg.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsplash_0WxjDT_3Tsw.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">IMG_5887.jpg</t>
@@ -2696,10 +2708,10 @@
         <v>33</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q3" s="2" t="s">
         <v>25</v>
@@ -2717,19 +2729,19 @@
         <v>Wed</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J4" s="5" t="str">
         <f aca="false">I4&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C15</f>
@@ -2737,16 +2749,16 @@
       </c>
       <c r="K4" s="4"/>
       <c r="L4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P4" s="4"/>
       <c r="Q4" s="2" t="s">
@@ -2765,19 +2777,19 @@
         <v>Thu</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J5" s="5" t="str">
         <f aca="false">I5&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C16</f>
@@ -2785,16 +2797,16 @@
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P5" s="4"/>
       <c r="Q5" s="2" t="s">
@@ -2816,16 +2828,16 @@
         <v>16</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J6" s="5" t="str">
         <f aca="false">I6&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C17</f>
@@ -2833,16 +2845,16 @@
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P6" s="4"/>
       <c r="Q6" s="2" t="s">
@@ -2861,19 +2873,19 @@
         <v>Mon</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J7" s="5" t="str">
         <f aca="false">I7&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C18</f>
@@ -2881,16 +2893,16 @@
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P7" s="4"/>
       <c r="Q7" s="2" t="s">
@@ -2912,16 +2924,16 @@
         <v>16</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J8" s="5" t="str">
         <f aca="false">I8&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C19</f>
@@ -2929,16 +2941,16 @@
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P8" s="4"/>
       <c r="Q8" s="2" t="s">
@@ -2957,19 +2969,19 @@
         <v>Wed</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="5" t="str">
         <f aca="false">I9&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C20</f>
@@ -2977,16 +2989,16 @@
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P9" s="4"/>
       <c r="Q9" s="2" t="s">
@@ -3005,19 +3017,19 @@
         <v>Thu</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J10" s="5" t="str">
         <f aca="false">I10&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C21</f>
@@ -3025,16 +3037,16 @@
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="2" t="s">
@@ -3056,16 +3068,16 @@
         <v>16</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J11" s="5" t="str">
         <f aca="false">I11&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C22</f>
@@ -3073,16 +3085,16 @@
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="2" t="s">
@@ -3104,16 +3116,16 @@
         <v>26</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J12" s="5" t="str">
         <f aca="false">I12&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C23</f>
@@ -3121,16 +3133,16 @@
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P12" s="4"/>
       <c r="Q12" s="2" t="s">
@@ -3152,16 +3164,16 @@
         <v>16</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J13" s="5" t="str">
         <f aca="false">I13&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C24</f>
@@ -3169,16 +3181,16 @@
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P13" s="4"/>
       <c r="Q13" s="2" t="s">
@@ -3197,19 +3209,19 @@
         <v>Wed</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J14" s="5" t="str">
         <f aca="false">I14&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C25</f>
@@ -3217,16 +3229,16 @@
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="2" t="s">
@@ -3245,19 +3257,19 @@
         <v>Thu</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J15" s="5" t="str">
         <f aca="false">I15&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C26</f>
@@ -3265,16 +3277,16 @@
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P15" s="4"/>
       <c r="Q15" s="2" t="s">
@@ -3296,16 +3308,16 @@
         <v>16</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J16" s="5" t="str">
         <f aca="false">I16&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C27</f>
@@ -3313,16 +3325,16 @@
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P16" s="4"/>
       <c r="Q16" s="2" t="s">
@@ -3344,16 +3356,16 @@
         <v>26</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>29</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J17" s="5" t="str">
         <f aca="false">I17&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C28</f>
@@ -3361,19 +3373,19 @@
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q17" s="2" t="s">
         <v>25</v>
@@ -3394,16 +3406,16 @@
         <v>16</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J18" s="5" t="str">
         <f aca="false">I18&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C29</f>
@@ -3411,16 +3423,16 @@
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P18" s="4"/>
       <c r="Q18" s="2" t="s">
@@ -3439,19 +3451,19 @@
         <v>Wed</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J19" s="5" t="str">
         <f aca="false">I19&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C30</f>
@@ -3459,16 +3471,16 @@
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P19" s="4"/>
       <c r="Q19" s="2" t="s">
@@ -3487,19 +3499,19 @@
         <v>Thu</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J20" s="5" t="str">
         <f aca="false">I20&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C31</f>
@@ -3507,16 +3519,16 @@
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P20" s="4"/>
       <c r="Q20" s="2" t="s">
@@ -3538,10 +3550,10 @@
         <v>26</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>29</v>
@@ -3555,19 +3567,19 @@
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O21" s="4" t="s">
         <v>24</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>25</v>
@@ -3588,16 +3600,16 @@
         <v>16</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J22" s="5" t="str">
         <f aca="false">I22&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C33</f>
@@ -3605,13 +3617,13 @@
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O22" s="4" t="s">
         <v>24</v>
@@ -3633,19 +3645,19 @@
         <v>Tue</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J23" s="5" t="str">
         <f aca="false">I23&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C34</f>
@@ -3653,16 +3665,16 @@
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="P23" s="4"/>
       <c r="Q23" s="2" t="s">
@@ -3702,80 +3714,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>4</v>
@@ -3786,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D13" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F2</f>
@@ -3798,7 +3810,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D14" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F3</f>
@@ -3810,7 +3822,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D15" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F4</f>
@@ -3822,7 +3834,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D16" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F5</f>
@@ -3834,7 +3846,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D17" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F6</f>
@@ -3846,7 +3858,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D18" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F7</f>
@@ -3858,7 +3870,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D19" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F8</f>
@@ -3870,7 +3882,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D20" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F9</f>
@@ -3882,7 +3894,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D21" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F10</f>
@@ -3894,7 +3906,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D22" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F11</f>
@@ -3906,7 +3918,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D23" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F12</f>
@@ -3918,7 +3930,7 @@
         <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D24" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F13</f>
@@ -3930,7 +3942,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D25" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F14</f>
@@ -3942,7 +3954,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D26" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F15</f>
@@ -3954,7 +3966,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D27" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F16</f>
@@ -3966,7 +3978,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D28" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F17</f>
@@ -3978,7 +3990,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D29" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F18</f>
@@ -3990,7 +4002,7 @@
         <v>18</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D30" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F19</f>
@@ -4002,7 +4014,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D31" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F20</f>
@@ -4014,7 +4026,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D32" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F21</f>
@@ -4026,7 +4038,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D33" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F22</f>
@@ -4038,7 +4050,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D34" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F23</f>
@@ -4074,232 +4086,232 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F17" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -4332,35 +4344,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4371,19 +4383,19 @@
         <v>46328</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4394,19 +4406,19 @@
         <v>46329</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4417,19 +4429,19 @@
         <v>46330</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4440,19 +4452,19 @@
         <v>46331</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>265</v>
-      </c>
       <c r="F8" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4463,19 +4475,19 @@
         <v>46332</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>266</v>
-      </c>
       <c r="G9" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4486,19 +4498,19 @@
         <v>46335</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4509,19 +4521,19 @@
         <v>46336</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4532,19 +4544,19 @@
         <v>46337</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4555,19 +4567,19 @@
         <v>46338</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4578,19 +4590,19 @@
         <v>46339</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4601,19 +4613,19 @@
         <v>46342</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4624,19 +4636,19 @@
         <v>46343</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4647,19 +4659,19 @@
         <v>46344</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4670,19 +4682,19 @@
         <v>46345</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4693,19 +4705,19 @@
         <v>46346</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4716,19 +4728,19 @@
         <v>46349</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4739,19 +4751,19 @@
         <v>46350</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4762,19 +4774,19 @@
         <v>46351</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4785,19 +4797,19 @@
         <v>46352</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4808,19 +4820,19 @@
         <v>46353</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4831,19 +4843,19 @@
         <v>46356</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4854,19 +4866,19 @@
         <v>46357</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4877,19 +4889,19 @@
         <v>46357</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4900,24 +4912,24 @@
         <v>46357</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B30" s="9" t="str">
         <f aca="false">COUNTIF(G5:G28,"OK*")&amp;" of "&amp;COUNTA(G5:G28)</f>
@@ -4926,21 +4938,21 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4948,18 +4960,18 @@
         <v>1</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -4989,26 +5001,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5016,13 +5028,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5030,13 +5042,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5044,13 +5056,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5058,13 +5070,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5072,13 +5084,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5086,13 +5098,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5100,13 +5112,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5114,13 +5126,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5128,13 +5140,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5142,13 +5154,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5156,13 +5168,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5170,13 +5182,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5184,13 +5196,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -5226,53 +5238,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6443,7 +6455,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B28" s="9" t="str">
         <f aca="false">COUNTIF(M5:M26,"Pass")&amp;" of "&amp;COUNTA(A5:A26)</f>
@@ -6452,7 +6464,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6460,7 +6472,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6474,7 +6486,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" s="2" t="n">
         <f aca="false">COUNTIF('preferredfencesolutions.com'!$E$2:$E$23,"FAQ")</f>
@@ -6483,7 +6495,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="2" t="n">
         <f aca="false">COUNTIF('preferredfencesolutions.com'!$E$2:$E$23,"Local")</f>
@@ -6501,7 +6513,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B36" s="2" t="n">
         <f aca="false">SUM(B32:B35)</f>

--- a/deliverables/gbp-calendars/Preferred-Fence-GBP-Monthly-Calendar-Nov-2026.xlsx
+++ b/deliverables/gbp-calendars/Preferred-Fence-GBP-Monthly-Calendar-Nov-2026.xlsx
@@ -12,8 +12,9 @@
     <sheet name="Settings" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Banner &amp; Brand Kit" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Image Rights Check" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="GBP Guidelines" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="QA Cross-Check" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Website Offers Check" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="GBP Guidelines" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="QA Cross-Check" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'preferredfencesolutions.com'!$B$1:$Q$23</definedName>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="391">
   <si>
     <t xml:space="preserve">Week</t>
   </si>
@@ -120,7 +121,7 @@
   </si>
   <si>
     <t xml:space="preserve">Planning a new fence or a fence replacement before spring? Book a free on-site estimate with Preferred Fence Solutions.
-We measure your yard, talk through materials, height and gates, and give you a clear written quote. Wood, vinyl, ornamental iron, chain link and SimTek options are available across Oklahoma City, Edmond, Yukon, Mustang and Nichols Hills.
+We measure your yard, talk through materials, height and gates, and give you a clear written quote. Wood, vinyl, ornamental iron, chain link and SimTek options are available across Oklahoma City, Edmond, Yukon, Mustang and Nichols Hills. Financing is available for larger projects.
 Tap View offer to request your free estimate.</t>
   </si>
   <si>
@@ -145,7 +146,7 @@
     <t xml:space="preserve">Business's own photo from its website (client to confirm ownership).</t>
   </si>
   <si>
-    <t xml:space="preserve">Offer dates: Nov 3 to Nov 30, 2026. Terms: free estimate within the service area; no obligation.</t>
+    <t xml:space="preserve">Offer dates: Nov 3 to Nov 30, 2026 (confirm). Terms: free estimate on all fence and gate projects (as stated on the website); no obligation. Financing available for larger projects.</t>
   </si>
   <si>
     <t xml:space="preserve">FAQ</t>
@@ -250,7 +251,7 @@
   </si>
   <si>
     <t xml:space="preserve">Looking for security that still looks elegant from the street?
-Preferred Fence Solutions installs Ameristar ornamental iron fences and gates for homes in Oklahoma City, Edmond and the surrounding metro. We have installed iron fences from 4 to 6 feet tall and can add decorative finials, scrolls and custom gates.
+Preferred Fence Solutions installs Ameristar ornamental iron fences and gates for homes in Oklahoma City, Edmond and the surrounding metro. We have installed iron fences from 4 to 6 feet tall and can add decorative finials, scrolls and custom gates. Ameristar products come backed by a 20-year warranty.
 Ornamental iron is a popular choice for front yards, pools and retaining walls. Tap Learn more to see recent projects.</t>
   </si>
   <si>
@@ -450,21 +451,21 @@
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/05/6-tall-white-vinyl-privacy-fence-.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Free Fence Design and Planning Consultation</t>
+    <t xml:space="preserve">Fence Design Help With Every Free Estimate</t>
   </si>
   <si>
     <t xml:space="preserve">Thinking about a new fence for spring? Not sure which style, material or height is right for your property?
-Book a free design and planning consultation with Preferred Fence Solutions. We will walk your yard, talk through privacy, pets, gates and budget, and recommend the best option for your home before we schedule your install.
-Tap View offer to book your consultation.</t>
+Preferred Fence Solutions offers free estimates on all fence and gate projects, and our team helps you plan the design. We will walk your yard, talk through privacy, pets, gates and budget, and recommend the best option for your home. Financing is available for larger projects, so ask about it during your estimate.
+Tap View offer to book your free estimate.</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/fence-design-planning/</t>
   </si>
   <si>
-    <t xml:space="preserve">Tag: Free Consultation
+    <t xml:space="preserve">Tag: Free Estimate
 Headline: Plan Your Spring Fence Now
-Sub-line: Free design and planning consultation
-Button: Book Your Consultation</t>
+Sub-line: Design help with every free estimate
+Button: Book Your Free Estimate</t>
   </si>
   <si>
     <t xml:space="preserve">2026-11-23_gbp-post-16_1200x900.png</t>
@@ -473,7 +474,7 @@
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2021/12/desing-and-planning.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">Offer dates: Nov 23 to Dec 31, 2026 (confirm). Terms: consultation and estimate are free; no obligation.</t>
+    <t xml:space="preserve">Offer dates: Nov 23 to Dec 31, 2026 (confirm). Terms: free estimate on all fence and gate projects (as stated on the website); no obligation. Financing available for larger projects.</t>
   </si>
   <si>
     <t xml:space="preserve">Residential Gates: Width and Placement</t>
@@ -1061,6 +1062,102 @@
   </si>
   <si>
     <t xml:space="preserve">Note: photos on the business's own website are treated as owned by the business. Ask the client to confirm they took these photos or hold the rights. Unsplash photos can be used commercially without credit, but do not show people or brands in a way that suggests endorsement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offers on the website vs. this calendar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every page of preferredfencesolutions.com was checked on Oct 26, 2026. Posts only promote offers the website states.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Offer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exact wording on the website</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used in post #</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free estimate on all projects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We offer free estimates on all fence &amp; gate requests.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1, 2 (Offer post), 4, 12, 13, 14, 15, 16 (Offer post), 20 (Offer post)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live on many pages. This is the main offer for this business.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financing for larger projects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financing options are available for larger projects; ask us during your free estimate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://preferredfencesolutions.com/why-preferred-fence-solutions-is-oklahoma-citys-trusted-fence-contractor/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2, 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added after this check. Rates and terms are not on the website, so posts do not quote any.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1-year warranty on fences and gates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">We warranty all of our fences, including gates, for an entire year.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14, 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Used as stated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20-year warranty on Ameristar iron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">They also come backed by a 20-year warranty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Added to the Ameristar post after this check.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design and planning help</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you know you are in need of a fence ... but you're unsure of what style, design, or material to use, we can help!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The website does not call this a free consultation. Post 16 was changed from 'Free Design Consultation' to 'Design Help With Every Free Estimate'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discounts / coupons / % off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All 141 pages checked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not used</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No price discount, coupon, seasonal sale or military/senior discount is on the website.</t>
   </si>
   <si>
     <t xml:space="preserve">Google Business Profile post rules applied to this calendar</t>
@@ -3982,7 +4079,7 @@
       </c>
       <c r="D28" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F17</f>
-        <v>Free Fence Design and Planning Consultation</v>
+        <v>Fence Design Help With Every Free Estimate</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4990,13 +5087,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5014,195 +5113,139 @@
         <v>299</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>243</v>
+        <v>309</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>311</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>105</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>319</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>64</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>117</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="E10" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -5217,6 +5260,237 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:D17"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="55"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>243</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
@@ -5238,12 +5512,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>342</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>343</v>
+        <v>375</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5254,37 +5528,37 @@
         <v>259</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>344</v>
+        <v>376</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>345</v>
+        <v>377</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>346</v>
+        <v>378</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>347</v>
+        <v>379</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>348</v>
+        <v>380</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>351</v>
+        <v>383</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>354</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5350,7 +5624,7 @@
       </c>
       <c r="C6" s="2" t="n">
         <f aca="false">LEN('preferredfencesolutions.com'!G3)</f>
-        <v>405</v>
+        <v>449</v>
       </c>
       <c r="D6" s="2" t="str">
         <f aca="false">IF(LEN('preferredfencesolutions.com'!G3)&lt;=1500,"Pass","Fail")</f>
@@ -5615,7 +5889,7 @@
       </c>
       <c r="C11" s="2" t="n">
         <f aca="false">LEN('preferredfencesolutions.com'!G8)</f>
-        <v>433</v>
+        <v>487</v>
       </c>
       <c r="D11" s="2" t="str">
         <f aca="false">IF(LEN('preferredfencesolutions.com'!G8)&lt;=1500,"Pass","Fail")</f>
@@ -6092,7 +6366,7 @@
       </c>
       <c r="C20" s="2" t="n">
         <f aca="false">LEN('preferredfencesolutions.com'!G17)</f>
-        <v>375</v>
+        <v>469</v>
       </c>
       <c r="D20" s="2" t="str">
         <f aca="false">IF(LEN('preferredfencesolutions.com'!G17)&lt;=1500,"Pass","Fail")</f>
@@ -6455,7 +6729,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>355</v>
+        <v>387</v>
       </c>
       <c r="B28" s="9" t="str">
         <f aca="false">COUNTIF(M5:M26,"Pass")&amp;" of "&amp;COUNTA(A5:A26)</f>
@@ -6464,7 +6738,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>356</v>
+        <v>388</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6472,7 +6746,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>357</v>
+        <v>389</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6513,7 +6787,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>358</v>
+        <v>390</v>
       </c>
       <c r="B36" s="2" t="n">
         <f aca="false">SUM(B32:B35)</f>

--- a/deliverables/gbp-calendars/Preferred-Fence-GBP-Monthly-Calendar-Nov-2026.xlsx
+++ b/deliverables/gbp-calendars/Preferred-Fence-GBP-Monthly-Calendar-Nov-2026.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="395">
   <si>
     <t xml:space="preserve">Week</t>
   </si>
@@ -586,7 +586,10 @@
     <t xml:space="preserve">2026-11-30_gbp-post-21_1200x900.png</t>
   </si>
   <si>
-    <t xml:space="preserve">https://unsplash.com/photos/0WxjDT_3Tsw (Unsplash licence)</t>
+    <t xml:space="preserve">AI-generated with Ideogram (illustrative): https://ideogram.ai/g/D6aNN7JVRvKA3FneilN_8A/0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-generated image (Ideogram). Illustrative only, not the client's own project. Confirm commercial use under the Ideogram account plan terms.</t>
   </si>
   <si>
     <t xml:space="preserve">Thank You, Oklahoma City</t>
@@ -1013,7 +1016,16 @@
     <t xml:space="preserve">unsplash_LbkIbkMPKjg.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">unsplash_0WxjDT_3Tsw.jpg</t>
+    <t xml:space="preserve">ai_ideogram_xFZhaXmcWVantneRPPXhuQ.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-generated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated with Ideogram for this banner; shows a stone-look fence style, not a real job by the client; No photographer credit, stock agency tag or watermark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK: AI image, client to approve</t>
   </si>
   <si>
     <t xml:space="preserve">IMG_5887.jpg</t>
@@ -1061,7 +1073,7 @@
     <t xml:space="preserve">IMG_5914.jpg and IMG_0730001.jpg (own project photos)</t>
   </si>
   <si>
-    <t xml:space="preserve">Note: photos on the business's own website are treated as owned by the business. Ask the client to confirm they took these photos or hold the rights. Unsplash photos can be used commercially without credit, but do not show people or brands in a way that suggests endorsement.</t>
+    <t xml:space="preserve">Note: photos on the business's own website are treated as owned by the business. Ask the client to confirm they took these photos or hold the rights. Unsplash photos can be used commercially without credit, but do not show people or brands in a way that suggests endorsement. AI-generated images are illustrations only: never present them as the client's own finished work, and get client approval before posting.</t>
   </si>
   <si>
     <t xml:space="preserve">Offers on the website vs. this calendar</t>
@@ -1256,7 +1268,7 @@
     <t xml:space="preserve">Photos must follow the photo policy: real, relevant to the business, not misleading.</t>
   </si>
   <si>
-    <t xml:space="preserve">Every banner uses a real photo from the business's own website (one HG post uses a licensed Unsplash photo). Overlay text is short (headline plus one line), with no phone numbers, emails, prices or claims that are not on the website.</t>
+    <t xml:space="preserve">Banners use the business's own website photos where one fits the topic. Where none fits, a free Unsplash photo is used, and one Preferred Fence banner (SimTek) uses an AI-generated illustration, marked on the Image Rights Check tab. Overlay text is short (headline plus one line), with no phone numbers, emails, prices or claims that are not on the website.</t>
   </si>
   <si>
     <t xml:space="preserve">Recommended post image: JPG or PNG, 10 KB to 5 MB, at least 400 x 300 px, 4:3 ratio displays best.</t>
@@ -3723,7 +3735,7 @@
         <v>150</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="P22" s="4"/>
       <c r="Q22" s="2" t="s">
@@ -3745,16 +3757,16 @@
         <v>43</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J23" s="5" t="str">
         <f aca="false">I23&amp;"?utm_source="&amp;Settings!$C$5&amp;"&amp;utm_medium="&amp;Settings!$C$6&amp;"&amp;utm_campaign="&amp;Settings!$C$7&amp;"&amp;utm_content="&amp;Settings!C34</f>
@@ -3762,13 +3774,13 @@
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O23" s="4" t="s">
         <v>34</v>
@@ -3811,80 +3823,80 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>4</v>
@@ -3895,7 +3907,7 @@
         <v>1</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D13" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F2</f>
@@ -3907,7 +3919,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D14" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F3</f>
@@ -3919,7 +3931,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D15" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F4</f>
@@ -3931,7 +3943,7 @@
         <v>4</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D16" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F5</f>
@@ -3943,7 +3955,7 @@
         <v>5</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D17" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F6</f>
@@ -3955,7 +3967,7 @@
         <v>6</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D18" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F7</f>
@@ -3967,7 +3979,7 @@
         <v>7</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D19" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F8</f>
@@ -3979,7 +3991,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D20" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F9</f>
@@ -3991,7 +4003,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D21" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F10</f>
@@ -4003,7 +4015,7 @@
         <v>10</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D22" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F11</f>
@@ -4015,7 +4027,7 @@
         <v>11</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D23" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F12</f>
@@ -4027,7 +4039,7 @@
         <v>12</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D24" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F13</f>
@@ -4039,7 +4051,7 @@
         <v>13</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D25" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F14</f>
@@ -4051,7 +4063,7 @@
         <v>14</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D26" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F15</f>
@@ -4063,7 +4075,7 @@
         <v>15</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D27" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F16</f>
@@ -4075,7 +4087,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D28" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F17</f>
@@ -4087,7 +4099,7 @@
         <v>17</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D29" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F18</f>
@@ -4099,7 +4111,7 @@
         <v>18</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D30" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F19</f>
@@ -4111,7 +4123,7 @@
         <v>19</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D31" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F20</f>
@@ -4123,7 +4135,7 @@
         <v>20</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D32" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F21</f>
@@ -4135,7 +4147,7 @@
         <v>21</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D33" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F22</f>
@@ -4147,7 +4159,7 @@
         <v>22</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D34" s="4" t="str">
         <f aca="false">'preferredfencesolutions.com'!F23</f>
@@ -4183,232 +4195,232 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F15" s="11"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F17" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -4441,35 +4453,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4480,19 +4492,19 @@
         <v>46328</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4503,19 +4515,19 @@
         <v>46329</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4526,19 +4538,19 @@
         <v>46330</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4549,19 +4561,19 @@
         <v>46331</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4572,19 +4584,19 @@
         <v>46332</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>55</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4595,19 +4607,19 @@
         <v>46335</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4618,19 +4630,19 @@
         <v>46336</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>67</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4641,19 +4653,19 @@
         <v>46337</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>73</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4664,19 +4676,19 @@
         <v>46338</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>79</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4687,19 +4699,19 @@
         <v>46339</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>85</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4710,19 +4722,19 @@
         <v>46342</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>91</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4733,19 +4745,19 @@
         <v>46343</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>97</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4756,19 +4768,19 @@
         <v>46344</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4779,19 +4791,19 @@
         <v>46345</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>108</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4802,19 +4814,19 @@
         <v>46346</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>114</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4825,19 +4837,19 @@
         <v>46349</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>120</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4848,19 +4860,19 @@
         <v>46350</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>127</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4871,19 +4883,19 @@
         <v>46351</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4894,19 +4906,19 @@
         <v>46352</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>138</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4917,19 +4929,19 @@
         <v>46353</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>143</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4940,19 +4952,19 @@
         <v>46356</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>150</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>266</v>
+        <v>292</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>268</v>
+        <v>294</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4963,19 +4975,19 @@
         <v>46357</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4986,19 +4998,19 @@
         <v>46357</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5009,24 +5021,24 @@
         <v>46357</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B30" s="9" t="str">
         <f aca="false">COUNTIF(G5:G28,"OK*")&amp;" of "&amp;COUNTA(G5:G28)</f>
@@ -5035,21 +5047,21 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5057,18 +5069,18 @@
         <v>1</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
   </sheetData>
@@ -5100,32 +5112,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5133,19 +5145,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>105</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5153,19 +5165,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5173,19 +5185,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5193,19 +5205,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>64</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5213,19 +5225,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>117</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5233,19 +5245,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -5275,26 +5287,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5302,13 +5314,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5316,13 +5328,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5330,13 +5342,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5344,13 +5356,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5358,13 +5370,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5372,13 +5384,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5386,13 +5398,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5400,13 +5412,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5414,13 +5426,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5428,13 +5440,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>367</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5442,27 +5454,27 @@
         <v>11</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5470,13 +5482,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -5512,53 +5524,53 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6729,7 +6741,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B28" s="9" t="str">
         <f aca="false">COUNTIF(M5:M26,"Pass")&amp;" of "&amp;COUNTA(A5:A26)</f>
@@ -6738,7 +6750,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6746,7 +6758,7 @@
         <v>3</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6787,7 +6799,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="B36" s="2" t="n">
         <f aca="false">SUM(B32:B35)</f>

--- a/deliverables/gbp-calendars/Preferred-Fence-GBP-Monthly-Calendar-Nov-2026.xlsx
+++ b/deliverables/gbp-calendars/Preferred-Fence-GBP-Monthly-Calendar-Nov-2026.xlsx
@@ -102,7 +102,8 @@
 Button: Free Repair Estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-02_gbp-post-01_1200x900.png</t>
+    <t xml:space="preserve">2026-11-02_gbp-post-01_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://unsplash.com/photos/km_VQEFOV20 (Unsplash licence)</t>
@@ -137,7 +138,8 @@
 Button: Book Your Free Estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-03_gbp-post-02_1200x900.png</t>
+    <t xml:space="preserve">2026-11-03_gbp-post-02_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/05/IMG_5913.jpg</t>
@@ -169,7 +171,8 @@
 Button: More Fence FAQs</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-04_gbp-post-03_1200x900.png</t>
+    <t xml:space="preserve">2026-11-04_gbp-post-03_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/10/Stained-Western-Red-Cedar-with-Cap-and-Trim-with-a-1x6-Kickboard.jpg</t>
@@ -195,7 +198,8 @@
 Button: Free Estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-05_gbp-post-04_1200x900.png</t>
+    <t xml:space="preserve">2026-11-05_gbp-post-04_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/01/IMG_01991-2.jpg</t>
@@ -218,7 +222,8 @@
 Button: See Fence Styles</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-06_gbp-post-05_1200x900.png</t>
+    <t xml:space="preserve">2026-11-06_gbp-post-05_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/03/6-tall-Cap-and-Trim-Total-Privacy-Board-on-Board.-.jpeg</t>
@@ -241,7 +246,8 @@
 Button: Read the Guide</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-09_gbp-post-06_1200x900.png</t>
+    <t xml:space="preserve">2026-11-09_gbp-post-06_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/06/new-vs-old.jpeg</t>
@@ -264,7 +270,8 @@
 Button: See Recent Projects</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-10_gbp-post-07_1200x900.png</t>
+    <t xml:space="preserve">2026-11-10_gbp-post-07_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/05/Arched-ornamental-iron-double-gate-custom-Letter-2.jpg</t>
@@ -287,7 +294,8 @@
 Button: Read the Local Guide</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-11_gbp-post-08_1200x900.png</t>
+    <t xml:space="preserve">2026-11-11_gbp-post-08_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2021/12/IMG_8799-scaled.jpg</t>
@@ -310,7 +318,8 @@
 Button: Read the Article</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-12_gbp-post-09_1200x900.png</t>
+    <t xml:space="preserve">2026-11-12_gbp-post-09_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2021/12/IMG_5922.jpg</t>
@@ -333,7 +342,8 @@
 Button: Commercial Estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-13_gbp-post-10_1200x900.png</t>
+    <t xml:space="preserve">2026-11-13_gbp-post-10_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2026/05/4800-S-Sunnylane-Rd_Completed-Pic-5-scaled.jpg</t>
@@ -356,7 +366,8 @@
 Button: See Doggie Windows</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-16_gbp-post-11_1200x900.png</t>
+    <t xml:space="preserve">2026-11-16_gbp-post-11_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/07/bassethound-doggie-window.jpeg</t>
@@ -379,7 +390,8 @@
 Button: Get a Free Quote</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-17_gbp-post-12_1200x900.png</t>
+    <t xml:space="preserve">2026-11-17_gbp-post-12_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/01/4-black-chain-link.jpg</t>
@@ -399,7 +411,8 @@
 Button: Get a Free Estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-18_gbp-post-13_1200x900.png</t>
+    <t xml:space="preserve">2026-11-18_gbp-post-13_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/03/1x4x6-Western-Red-Cedar-with-Cap-and-Trim-scaled.jpg</t>
@@ -422,7 +435,8 @@
 Button: Free Estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-19_gbp-post-14_1200x900.png</t>
+    <t xml:space="preserve">2026-11-19_gbp-post-14_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2021/12/IMG_5879.jpg</t>
@@ -445,7 +459,8 @@
 Button: See Vinyl Styles</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-20_gbp-post-15_1200x900.png</t>
+    <t xml:space="preserve">2026-11-20_gbp-post-15_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/05/6-tall-white-vinyl-privacy-fence-.jpg</t>
@@ -468,7 +483,8 @@
 Button: Book Your Free Estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-23_gbp-post-16_1200x900.png</t>
+    <t xml:space="preserve">2026-11-23_gbp-post-16_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2021/12/desing-and-planning.jpg</t>
@@ -494,7 +510,8 @@
 Button: Read the Gate Guide</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-24_gbp-post-17_1200x900.png</t>
+    <t xml:space="preserve">2026-11-24_gbp-post-17_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/04/o-3.jpg</t>
@@ -517,7 +534,8 @@
 Button: See What to Expect</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-25_gbp-post-18_1200x900.png</t>
+    <t xml:space="preserve">2026-11-25_gbp-post-18_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">Happy Thanksgiving from Preferred Fence Solutions</t>
@@ -537,7 +555,8 @@
 Button: </t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-26_gbp-post-19_1200x900.png</t>
+    <t xml:space="preserve">2026-11-26_gbp-post-19_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2022/01/o-8.jpg</t>
@@ -557,7 +576,8 @@
 Button: Book a Free Estimate</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-27_gbp-post-20_1200x900.png</t>
+    <t xml:space="preserve">2026-11-27_gbp-post-20_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://unsplash.com/photos/LbkIbkMPKjg (Unsplash licence)</t>
@@ -583,7 +603,8 @@
 Button: Is SimTek Right for You?</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-11-30_gbp-post-21_1200x900.png</t>
+    <t xml:space="preserve">2026-11-30_gbp-post-21_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">AI-generated with Ideogram (illustrative): https://ideogram.ai/g/D6aNN7JVRvKA3FneilN_8A/0</t>
@@ -609,7 +630,8 @@
 Button: See Our Awards</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-12-01_gbp-post-22_1200x900.png</t>
+    <t xml:space="preserve">2026-12-01_gbp-post-22_1200x900.png
+(open in Google Drive)</t>
   </si>
   <si>
     <t xml:space="preserve">https://preferredfencesolutions.com/wp-content/uploads/2021/12/IMG_5887.jpg
@@ -2762,7 +2784,7 @@
       <c r="L2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="5" t="s">
         <v>22</v>
       </c>
       <c r="N2" s="4" t="s">
@@ -2810,7 +2832,7 @@
       <c r="L3" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="5" t="s">
         <v>32</v>
       </c>
       <c r="N3" s="4" t="s">
@@ -2860,7 +2882,7 @@
       <c r="L4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="5" t="s">
         <v>41</v>
       </c>
       <c r="N4" s="4" t="s">
@@ -2908,7 +2930,7 @@
       <c r="L5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="N5" s="4" t="s">
@@ -2956,7 +2978,7 @@
       <c r="L6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="M6" s="5" t="s">
         <v>54</v>
       </c>
       <c r="N6" s="4" t="s">
@@ -3004,7 +3026,7 @@
       <c r="L7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="M7" s="5" t="s">
         <v>60</v>
       </c>
       <c r="N7" s="4" t="s">
@@ -3052,7 +3074,7 @@
       <c r="L8" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="M8" s="5" t="s">
         <v>66</v>
       </c>
       <c r="N8" s="4" t="s">
@@ -3100,7 +3122,7 @@
       <c r="L9" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="M9" s="5" t="s">
         <v>72</v>
       </c>
       <c r="N9" s="4" t="s">
@@ -3148,7 +3170,7 @@
       <c r="L10" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="M10" s="4" t="s">
+      <c r="M10" s="5" t="s">
         <v>78</v>
       </c>
       <c r="N10" s="4" t="s">
@@ -3196,7 +3218,7 @@
       <c r="L11" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="M11" s="4" t="s">
+      <c r="M11" s="5" t="s">
         <v>84</v>
       </c>
       <c r="N11" s="4" t="s">
@@ -3244,7 +3266,7 @@
       <c r="L12" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="M12" s="4" t="s">
+      <c r="M12" s="5" t="s">
         <v>90</v>
       </c>
       <c r="N12" s="4" t="s">
@@ -3292,7 +3314,7 @@
       <c r="L13" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M13" s="4" t="s">
+      <c r="M13" s="5" t="s">
         <v>96</v>
       </c>
       <c r="N13" s="4" t="s">
@@ -3340,7 +3362,7 @@
       <c r="L14" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="M14" s="4" t="s">
+      <c r="M14" s="5" t="s">
         <v>101</v>
       </c>
       <c r="N14" s="4" t="s">
@@ -3388,7 +3410,7 @@
       <c r="L15" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="M15" s="4" t="s">
+      <c r="M15" s="5" t="s">
         <v>107</v>
       </c>
       <c r="N15" s="4" t="s">
@@ -3436,7 +3458,7 @@
       <c r="L16" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="M16" s="4" t="s">
+      <c r="M16" s="5" t="s">
         <v>113</v>
       </c>
       <c r="N16" s="4" t="s">
@@ -3484,7 +3506,7 @@
       <c r="L17" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="M17" s="5" t="s">
         <v>119</v>
       </c>
       <c r="N17" s="4" t="s">
@@ -3534,7 +3556,7 @@
       <c r="L18" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="M18" s="4" t="s">
+      <c r="M18" s="5" t="s">
         <v>126</v>
       </c>
       <c r="N18" s="4" t="s">
@@ -3582,7 +3604,7 @@
       <c r="L19" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="M19" s="4" t="s">
+      <c r="M19" s="5" t="s">
         <v>132</v>
       </c>
       <c r="N19" s="4" t="s">
@@ -3630,7 +3652,7 @@
       <c r="L20" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="M20" s="5" t="s">
         <v>137</v>
       </c>
       <c r="N20" s="4" t="s">
@@ -3678,7 +3700,7 @@
       <c r="L21" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="M21" s="4" t="s">
+      <c r="M21" s="5" t="s">
         <v>142</v>
       </c>
       <c r="N21" s="4" t="s">
@@ -3728,7 +3750,7 @@
       <c r="L22" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="M22" s="5" t="s">
         <v>149</v>
       </c>
       <c r="N22" s="4" t="s">
@@ -3776,7 +3798,7 @@
       <c r="L23" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="M23" s="4" t="s">
+      <c r="M23" s="5" t="s">
         <v>156</v>
       </c>
       <c r="N23" s="4" t="s">
@@ -3798,6 +3820,30 @@
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="M2" r:id="rId1" display="2026-11-02_gbp-post-01_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M3" r:id="rId2" display="2026-11-03_gbp-post-02_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M4" r:id="rId3" display="2026-11-04_gbp-post-03_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M5" r:id="rId4" display="2026-11-05_gbp-post-04_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M6" r:id="rId5" display="2026-11-06_gbp-post-05_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M7" r:id="rId6" display="2026-11-09_gbp-post-06_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M8" r:id="rId7" display="2026-11-10_gbp-post-07_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M9" r:id="rId8" display="2026-11-11_gbp-post-08_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M10" r:id="rId9" display="2026-11-12_gbp-post-09_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M11" r:id="rId10" display="2026-11-13_gbp-post-10_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M12" r:id="rId11" display="2026-11-16_gbp-post-11_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M13" r:id="rId12" display="2026-11-17_gbp-post-12_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M14" r:id="rId13" display="2026-11-18_gbp-post-13_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M15" r:id="rId14" display="2026-11-19_gbp-post-14_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M16" r:id="rId15" display="2026-11-20_gbp-post-15_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M17" r:id="rId16" display="2026-11-23_gbp-post-16_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M18" r:id="rId17" display="2026-11-24_gbp-post-17_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M19" r:id="rId18" display="2026-11-25_gbp-post-18_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M20" r:id="rId19" display="2026-11-26_gbp-post-19_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M21" r:id="rId20" display="2026-11-27_gbp-post-20_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M22" r:id="rId21" display="2026-11-30_gbp-post-21_1200x900.png&#10;(open in Google Drive)"/>
+    <hyperlink ref="M23" r:id="rId22" display="2026-12-01_gbp-post-22_1200x900.png&#10;(open in Google Drive)"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3805,7 +3851,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId23"/>
 </worksheet>
 </file>
 
